--- a/outputs/E_wrapped_contacts.xlsx
+++ b/outputs/E_wrapped_contacts.xlsx
@@ -10,25 +10,27 @@
     <sheet name="Data 1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Validation Report" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Page Audit" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Provenance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Read me" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cell Evidence" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Verification" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Constraints" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Repair Proposals" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Correction History" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Join Receipt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Provenance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Read me" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cell Evidence" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Verification" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Constraints" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Repair Proposals" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Correction History" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data 1'!$A$1:$D$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provenance'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cell Evidence'!$A$1:$M$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Verification'!$A$1:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Constraints'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Correction History'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Join Receipt'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Provenance'!$A$1:$E$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Read me'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Verification'!$A$1:$B$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Constraints'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Correction History'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -36,7 +38,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -86,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -98,6 +102,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -600,6 +607,79 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Excel row</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Supporting equations</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Caution</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
@@ -665,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -794,22 +874,154 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
+          <t>layout_review</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Nearby text-only continuation lines joined to keyed rows; source boxes retained.</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Verify the source page and reconstructed cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>semantic_type_mismatch</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Value '001' does not match the inferred phone role (header='Contact ID'; 0/3 populated values match).</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Compare with the source document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>semantic_type_mismatch</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Value '002' does not match the inferred phone role (header='Contact ID'; 0/3 populated values match).</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Compare with the source document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>semantic_type_mismatch</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Value '003' does not match the inferred phone role (header='Contact ID'; 0/3 populated values match).</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Compare with the source document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
           <t>candidate_disagreement</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Selected words; alternative text produced different content or shape.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Compare the page and highlighted data.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H4"/>
+  <autoFilter ref="A1:H8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -917,7 +1129,7 @@
         <v>0.92</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.013</v>
+        <v>0.029</v>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
@@ -959,7 +1171,7 @@
         <v>0.92</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.01</v>
+        <v>0.077</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
@@ -1001,7 +1213,7 @@
         <v>0.92</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.003</v>
+        <v>0.014</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -1018,7 +1230,7 @@
         <v>12</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>158.4</v>
@@ -1032,6 +1244,103 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Source pages</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Page joins</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Repeated headers removed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Split rows recovered</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PDF page</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Source rows on page</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Output rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1143,7 +1452,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1187,7 +1496,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.033</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="4" ht="119" customHeight="1">
@@ -1316,13 +1625,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1337,7 +1646,9 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="44" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="27" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1406,6 +1717,16 @@
           <t>Role</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Location status</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Location reason</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="17" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -1451,6 +1772,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -1496,6 +1827,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -1541,6 +1882,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1586,6 +1937,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -1631,6 +1992,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -1676,6 +2047,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -1718,7 +2099,17 @@
       <c r="L8" s="4" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>extracted</t>
+          <t>wrapped_continuation_join</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -1766,6 +2157,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -1811,6 +2212,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1856,6 +2267,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -1898,7 +2319,17 @@
       <c r="L12" s="4" t="inlineStr"/>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>extracted</t>
+          <t>wrapped_continuation_join</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -1946,6 +2377,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -1991,6 +2432,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -2036,6 +2487,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -2078,7 +2539,17 @@
       <c r="L16" s="4" t="inlineStr"/>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>extracted</t>
+          <t>wrapped_continuation_join</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -2126,23 +2597,33 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M17"/>
+  <autoFilter ref="A1:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
     <col width="65" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -2178,7 +2659,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>fcc51c545caa5de36c512cc96f19621b2fe99756b2a7c3560d65b39a160c4e48</t>
+          <t>7425a476b574699734d38fd6279e58fdd496ccb9b588922604bec84ff637b791</t>
         </is>
       </c>
     </row>
@@ -2217,37 +2698,39 @@
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>cells</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>12</v>
+          <t>Export type</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Draft Excel</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>cells with source boxes</t>
+          <t>Non-empty exported cells</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>equations</t>
+          <t>Cells with source boxes</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>equation checks</t>
+          <t>Cells requiring full-page evidence review</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
@@ -2257,30 +2740,80 @@
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>failed equation checks</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>0</v>
+          <t>Cell source-box coverage</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>cells</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>cells with source boxes</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>equations</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>equation checks</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>failed equation checks</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>proposals with multiple equations</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B17" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
+  <autoFilter ref="A1:B17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2345,77 +2878,4 @@
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Excel row</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Supporting equations</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Caution</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/outputs/E_wrapped_contacts.xlsx
+++ b/outputs/E_wrapped_contacts.xlsx
@@ -22,15 +22,15 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data 1'!$A$1:$D$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$Q$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Join Receipt'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Provenance'!$A$1:$E$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Read me'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$X$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Verification'!$A$1:$B$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Constraints'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Correction History'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Correction History'!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -682,59 +682,65 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Evidence ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Time UTC</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Table</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Excel row</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Before</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>After</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Previous hash</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Event hash</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1032,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1041,12 +1047,17 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="29" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="65" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1082,30 +1093,55 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Candidate ID</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Selection reason</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Selected</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Tables</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Cells</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
@@ -1129,29 +1165,48 @@
         <v>0.92</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.029</v>
+        <v>0.026</v>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
           <t>lines</t>
         </is>
       </c>
-      <c r="G2" s="4" t="b">
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>p001-c01</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>native-primary</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>sequential</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" s="4" t="inlineStr"/>
+      <c r="L2" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="M2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="N2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="O2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="P2" s="4" t="n">
         <v>-10000</v>
       </c>
-      <c r="L2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" s="4" t="n">
@@ -1171,31 +1226,50 @@
         <v>0.92</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.077</v>
+        <v>0.143</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G3" s="4" t="b">
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>p001-c02</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>native-independent-recovery</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>bounded-parallel</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" s="4" t="inlineStr"/>
+      <c r="L3" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="4" t="n">
+      <c r="M3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="P3" s="4" t="n">
         <v>95.40000000000001</v>
       </c>
-      <c r="L3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4" ht="17" customHeight="1">
+      <c r="Q3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
@@ -1213,32 +1287,55 @@
         <v>0.92</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.014</v>
+        <v>0.096</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>words</t>
         </is>
       </c>
-      <c r="G4" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="4" t="n">
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>p001-c03</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>native-independent-recovery</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>bounded-parallel</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Highest deterministic candidate key: trusted layout, credible content, structural quality, then validation-adjusted score; plan order breaks exact ties.</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="O4" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="P4" s="4" t="n">
         <v>158.4</v>
       </c>
-      <c r="L4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:Q4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1496,7 +1593,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.199</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="4" ht="119" customHeight="1">
@@ -1603,7 +1700,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Ctrl+click a linked data cell for its source bounding box and original readings.</t>
+          <t>Ctrl+click a linked data cell for its source box, confidence meaning, original readings, alternatives and correction count.</t>
         </is>
       </c>
     </row>
@@ -1631,985 +1728,1663 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="44" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="27" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="65" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="58" customWidth="1" min="16" max="16"/>
+    <col width="44" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
+    <col width="65" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Evidence ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Data sheet</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Excel row</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Working value</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Original extracted value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Original source reading</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Source page</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>x0</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>y0</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>x1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>y1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Engine</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>OCR score</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence type</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Recognition score</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence meaning</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Reading</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Initial reading</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence state</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Location status</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Location reason</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Corrections</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Alternative readings</t>
         </is>
       </c>
     </row>
     <row r="2" ht="17" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
+          <t>T1:H:C1</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Contact ID</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Contact ID</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Contact ID</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="J2" s="4" t="n">
         <v>52.06999999999999</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="K2" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="L2" s="4" t="n">
         <v>62.06999999999999</v>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>native-anchors</t>
         </is>
       </c>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>native_text</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="n"/>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>Text and geometry came directly from the PDF text layer.</t>
+        </is>
+      </c>
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>Contact ID</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr">
-        <is>
-          <t>header</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U2" s="4" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="V2" s="4" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="4" t="inlineStr"/>
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
+          <t>T1:H:C2</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="C3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>135</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="J3" s="4" t="n">
         <v>52.06999999999999</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="K3" s="4" t="n">
         <v>162.23</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>62.06999999999999</v>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>native-anchors</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>native_text</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>Text and geometry came directly from the PDF text layer.</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>header</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>T1:H:C3</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="C4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>280</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="J4" s="4" t="n">
         <v>52.06999999999999</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="K4" s="4" t="n">
         <v>320.01</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="L4" s="4" t="n">
         <v>62.06999999999999</v>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>native-anchors</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>native_text</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>Text and geometry came directly from the PDF text layer.</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>header</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="V4" s="4" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>T1:H:C4</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>520</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="J5" s="4" t="n">
         <v>52.06999999999999</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="K5" s="4" t="n">
         <v>538.89</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="L5" s="4" t="n">
         <v>62.06999999999999</v>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>native-anchors</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>native_text</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>Text and geometry came directly from the PDF text layer.</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>header</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>T1:R1:C1</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="C6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="J6" s="4" t="n">
         <v>87.06999999999999</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="K6" s="4" t="n">
         <v>51.68000000000001</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="L6" s="4" t="n">
         <v>97.06999999999999</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>native-anchors</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>native_text</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>Text and geometry came directly from the PDF text layer.</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="V6" s="4" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>T1:R1:C2</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Asha Rao</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Asha Rao</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Asha Rao</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4" t="n">
         <v>135</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="J7" s="4" t="n">
         <v>87.06999999999999</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="K7" s="4" t="n">
         <v>178.91</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="L7" s="4" t="n">
         <v>97.06999999999999</v>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>native-anchors</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>native_text</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>Text and geometry came directly from the PDF text layer.</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Asha Rao</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="V7" s="4" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>T1:R1:C3</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="C8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="D8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>12 Example Street Building B, second floor</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>12 Example Street Building B, second floor</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>12 Example Street Building B, second floor</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4" t="n">
         <v>280</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="J8" s="4" t="n">
         <v>87.06999999999999</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="K8" s="4" t="n">
         <v>385.05</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="L8" s="4" t="n">
         <v>110.07</v>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>native-anchors</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>native_text</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>Text and geometry came directly from the PDF text layer.</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>12 Example Street Building B, second floor</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr">
         <is>
           <t>wrapped_continuation_join</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="V8" s="4" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>T1:R1:C4</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="C9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="D9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="4" t="n">
         <v>520</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="J9" s="4" t="n">
         <v>87.06999999999999</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="K9" s="4" t="n">
         <v>543.3499999999999</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="L9" s="4" t="n">
         <v>97.06999999999999</v>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>native-anchors</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>native_text</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>Text and geometry came directly from the PDF text layer.</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="V9" s="4" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>T1:R2:C1</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="C10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="J10" s="4" t="n">
         <v>135.07</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="K10" s="4" t="n">
         <v>51.68000000000001</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="L10" s="4" t="n">
         <v>145.07</v>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>native-anchors</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>native_text</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>Text and geometry came directly from the PDF text layer.</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="R10" s="4" t="inlineStr"/>
+      <c r="S10" s="4" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="V10" s="4" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t>T1:R2:C2</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="C11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="D11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Hari Sen</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Hari Sen</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Hari Sen</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="4" t="n">
         <v>135</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="J11" s="4" t="n">
         <v>135.07</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="K11" s="4" t="n">
         <v>173.9</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="L11" s="4" t="n">
         <v>145.07</v>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>native-anchors</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>native_text</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>Text and geometry came directly from the PDF text layer.</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>Hari Sen</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="V11" s="4" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>T1:R2:C3</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>13 Example Street Building B, second floor</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>13 Example Street Building B, second floor</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>13 Example Street Building B, second floor</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="4" t="n">
         <v>280</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="J12" s="4" t="n">
         <v>135.07</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="K12" s="4" t="n">
         <v>385.05</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="L12" s="4" t="n">
         <v>158.07</v>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>native-anchors</t>
         </is>
       </c>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>native_text</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>Text and geometry came directly from the PDF text layer.</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>13 Example Street Building B, second floor</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="R12" s="4" t="inlineStr"/>
+      <c r="S12" s="4" t="inlineStr">
         <is>
           <t>wrapped_continuation_join</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="V12" s="4" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>T1:R2:C4</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="C13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="D13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="4" t="n">
         <v>520</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="J13" s="4" t="n">
         <v>135.07</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="K13" s="4" t="n">
         <v>545.01</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="L13" s="4" t="n">
         <v>145.07</v>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>native-anchors</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>native_text</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>Text and geometry came directly from the PDF text layer.</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>Kochi</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="R13" s="4" t="inlineStr"/>
+      <c r="S13" s="4" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="V13" s="4" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>T1:R3:C1</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="C14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="J14" s="4" t="n">
         <v>183.07</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="K14" s="4" t="n">
         <v>51.68000000000001</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="L14" s="4" t="n">
         <v>193.07</v>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>native-anchors</t>
         </is>
       </c>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>native_text</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>Text and geometry came directly from the PDF text layer.</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>003</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="R14" s="4" t="inlineStr"/>
+      <c r="S14" s="4" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="V14" s="4" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="4" t="inlineStr"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>T1:R3:C2</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="C15" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="D15" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Mira Das</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Mira Das</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Mira Das</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="4" t="n">
         <v>135</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="J15" s="4" t="n">
         <v>183.07</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="K15" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="L15" s="4" t="n">
         <v>193.07</v>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>native-anchors</t>
         </is>
       </c>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>native_text</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="n"/>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>Text and geometry came directly from the PDF text layer.</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>Mira Das</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="R15" s="4" t="inlineStr"/>
+      <c r="S15" s="4" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U15" s="4" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="V15" s="4" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="4" t="inlineStr"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>T1:R3:C3</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="C16" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="D16" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>14 Example Street Building B, second floor</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>14 Example Street Building B, second floor</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>14 Example Street Building B, second floor</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="4" t="n">
         <v>280</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="J16" s="4" t="n">
         <v>183.07</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="K16" s="4" t="n">
         <v>385.05</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="L16" s="4" t="n">
         <v>206.07</v>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>native-anchors</t>
         </is>
       </c>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>native_text</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>Text and geometry came directly from the PDF text layer.</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
         <is>
           <t>14 Example Street Building B, second floor</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="R16" s="4" t="inlineStr"/>
+      <c r="S16" s="4" t="inlineStr">
         <is>
           <t>wrapped_continuation_join</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="V16" s="4" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t>T1:R3:C4</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>4</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Patna</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Patna</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Patna</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="4" t="n">
         <v>520</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="J17" s="4" t="n">
         <v>183.07</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="K17" s="4" t="n">
         <v>546.13</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="L17" s="4" t="n">
         <v>193.07</v>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>native-anchors</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>native_text</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="n"/>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>Text and geometry came directly from the PDF text layer.</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>Patna</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="R17" s="4" t="inlineStr"/>
+      <c r="S17" s="4" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="V17" s="4" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O17"/>
+  <autoFilter ref="A1:X17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2659,7 +3434,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>7425a476b574699734d38fd6279e58fdd496ccb9b588922604bec84ff637b791</t>
+          <t>d8a4647a29e3bad590dc228f145be942d1c4cef0aeb7af2ae703556a8bad1a04</t>
         </is>
       </c>
     </row>
